--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL_to_WP.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/TN WP 2026-27/SL_to_WP.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\TN WP 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Grv\Grv\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\TN WP 2026-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1008C265-9632-45E0-AA96-4CF8A5CDCA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A99F4C7-BEAA-45D6-9A0B-BB73CB055CB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="state" sheetId="2" r:id="rId3"/>
+    <sheet name="state" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +32,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="55">
+  <si>
+    <t>SEASON</t>
+  </si>
   <si>
     <t>Kharif</t>
   </si>
@@ -41,6 +43,9 @@
     <t>Rabi</t>
   </si>
   <si>
+    <t>CROP</t>
+  </si>
+  <si>
     <t>paddy_kar</t>
   </si>
   <si>
@@ -83,6 +88,9 @@
     <t>horsegram</t>
   </si>
   <si>
+    <t>CT</t>
+  </si>
+  <si>
     <t>--</t>
   </si>
   <si>
@@ -185,16 +193,10 @@
     <t>Ramanathapuram</t>
   </si>
   <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>As per sample list</t>
-  </si>
-  <si>
-    <t>As per Work Plan</t>
-  </si>
-  <si>
-    <t>As per work plan</t>
+    <t>Crop Total (SL)</t>
+  </si>
+  <si>
+    <t>Planned</t>
   </si>
 </sst>
 </file>
@@ -218,7 +220,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -249,43 +251,13 @@
         <bgColor rgb="FFE7FFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFFDD"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -303,137 +275,62 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,133 +346,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>560717</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>172528</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BC6D71A-DE2C-EBD3-413D-3679D1100D1B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="621102" y="181155"/>
-          <a:ext cx="10498347" cy="7056407"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>577970</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>172528</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAFC0BF0-475A-E093-F902-7A148F581A18}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="621102" y="7608498"/>
-          <a:ext cx="9894498" cy="7056408"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -863,250 +633,240 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ35"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AI36"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.625" customWidth="1"/>
-    <col min="2" max="2" width="23.625" customWidth="1"/>
-    <col min="3" max="17" width="3.625" customWidth="1"/>
-    <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5" style="17" customWidth="1"/>
-    <col min="20" max="34" width="3.625" customWidth="1"/>
-    <col min="35" max="35" width="4.375" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.25" style="17" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="9" customWidth="1"/>
+    <col min="1" max="1" width="3.5546875" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="34" width="3.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="29" t="s">
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-      <c r="AA1" s="30"/>
-      <c r="AB1" s="30"/>
-      <c r="AC1" s="30"/>
-      <c r="AD1" s="30"/>
-      <c r="AE1" s="30"/>
-      <c r="AF1" s="30"/>
-      <c r="AG1" s="30"/>
-      <c r="AH1" s="30"/>
-      <c r="AI1" s="30"/>
-      <c r="AJ1" s="30"/>
-    </row>
-    <row r="2" spans="1:36" ht="70" x14ac:dyDescent="0.25">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+    </row>
+    <row r="2" spans="1:35" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
+      <c r="B2" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="C2" s="9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J2" s="12"/>
       <c r="K2" s="11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q2" s="12"/>
       <c r="R2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="S2" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="T2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="U2" s="14"/>
+      <c r="V2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="14"/>
+      <c r="X2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="U2" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="V2" s="14"/>
-      <c r="W2" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI2" s="14"/>
-      <c r="AJ2" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AH2" s="14"/>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S3" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="T3" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AD3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG3" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AH3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="AI3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ3" s="5"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -1124,7 +884,7 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-      <c r="S4" s="16"/>
+      <c r="S4" s="6"/>
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -1140,15 +900,13 @@
       <c r="AF4" s="6"/>
       <c r="AG4" s="6"/>
       <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
-      <c r="AJ4" s="22"/>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -1178,41 +936,37 @@
       <c r="R5" s="4">
         <v>6</v>
       </c>
-      <c r="S5" s="16">
-        <f>SUM(C5:R5)</f>
-        <v>34</v>
-      </c>
+      <c r="S5" s="6"/>
       <c r="T5" s="6"/>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6">
-        <v>4</v>
-      </c>
+      <c r="W5" s="6">
+        <v>4</v>
+      </c>
+      <c r="X5" s="6"/>
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
       <c r="AA5" s="6"/>
       <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6">
-        <v>6</v>
-      </c>
+      <c r="AC5" s="6">
+        <v>6</v>
+      </c>
+      <c r="AD5" s="6"/>
       <c r="AE5" s="6"/>
       <c r="AF5" s="6"/>
       <c r="AG5" s="6"/>
       <c r="AH5" s="6"/>
-      <c r="AI5" s="6"/>
-      <c r="AJ5" s="22">
-        <f>SUM(T5:AI5)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI5">
+        <f>SUM(C5:AH5)</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -1232,14 +986,11 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="16">
-        <f t="shared" ref="S6:S33" si="0">SUM(C6:R6)</f>
-        <v>6</v>
-      </c>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6">
-        <v>6</v>
-      </c>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6">
+        <v>6</v>
+      </c>
+      <c r="U6" s="6"/>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
@@ -1250,23 +1001,22 @@
       <c r="AC6" s="6"/>
       <c r="AD6" s="6"/>
       <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6">
-        <v>4</v>
-      </c>
+      <c r="AF6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG6" s="6"/>
       <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="22">
-        <f t="shared" ref="AJ6:AJ33" si="1">SUM(T6:AI6)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI6">
+        <f t="shared" ref="AI6:AI33" si="0">SUM(C6:AH6)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4">
@@ -1302,19 +1052,16 @@
       <c r="R7" s="4">
         <v>4</v>
       </c>
-      <c r="S7" s="16">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="T7" s="6">
-        <v>4</v>
-      </c>
+      <c r="S7" s="6">
+        <v>4</v>
+      </c>
+      <c r="T7" s="6"/>
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6">
-        <v>4</v>
-      </c>
+      <c r="W7" s="6">
+        <v>4</v>
+      </c>
+      <c r="X7" s="6"/>
       <c r="Y7" s="6"/>
       <c r="Z7" s="6"/>
       <c r="AA7" s="6"/>
@@ -1322,23 +1069,22 @@
       <c r="AC7" s="6"/>
       <c r="AD7" s="6"/>
       <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6">
+      <c r="AF7" s="6">
         <v>12</v>
       </c>
+      <c r="AG7" s="6"/>
       <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-      <c r="AJ7" s="22">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
@@ -1370,19 +1116,16 @@
       </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
-      <c r="S8" s="16">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="T8" s="6">
-        <v>4</v>
-      </c>
+      <c r="S8" s="6">
+        <v>4</v>
+      </c>
+      <c r="T8" s="6"/>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6">
-        <v>4</v>
-      </c>
+      <c r="W8" s="6">
+        <v>4</v>
+      </c>
+      <c r="X8" s="6"/>
       <c r="Y8" s="6"/>
       <c r="Z8" s="6"/>
       <c r="AA8" s="6"/>
@@ -1390,23 +1133,22 @@
       <c r="AC8" s="6"/>
       <c r="AD8" s="6"/>
       <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6">
+      <c r="AF8" s="6">
         <v>20</v>
       </c>
+      <c r="AG8" s="6"/>
       <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
-      <c r="AJ8" s="22">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -1434,10 +1176,7 @@
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="16">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
+      <c r="S9" s="6"/>
       <c r="T9" s="6"/>
       <c r="U9" s="6"/>
       <c r="V9" s="6"/>
@@ -1450,23 +1189,22 @@
       <c r="AC9" s="6"/>
       <c r="AD9" s="6"/>
       <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="6">
+      <c r="AF9" s="6">
         <v>8</v>
       </c>
+      <c r="AG9" s="6"/>
       <c r="AH9" s="6"/>
-      <c r="AI9" s="6"/>
-      <c r="AJ9" s="22">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI9">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1504,51 +1242,49 @@
       <c r="R10" s="4">
         <v>4</v>
       </c>
-      <c r="S10" s="16">
-        <f t="shared" si="0"/>
-        <v>62</v>
+      <c r="S10" s="6">
+        <v>4</v>
       </c>
       <c r="T10" s="6">
         <v>4</v>
       </c>
       <c r="U10" s="6">
-        <v>4</v>
-      </c>
-      <c r="V10" s="6">
-        <v>6</v>
-      </c>
-      <c r="W10" s="6"/>
-      <c r="X10" s="24">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6">
+        <v>4</v>
+      </c>
+      <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
       <c r="Z10" s="6"/>
       <c r="AA10" s="6"/>
       <c r="AB10" s="6"/>
-      <c r="AC10" s="6"/>
-      <c r="AD10" s="24"/>
-      <c r="AE10" s="6"/>
+      <c r="AC10" s="6">
+        <v>4</v>
+      </c>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6">
+        <v>6</v>
+      </c>
       <c r="AF10" s="6">
-        <v>6</v>
-      </c>
-      <c r="AG10" s="6">
         <v>8</v>
       </c>
-      <c r="AH10" s="6"/>
-      <c r="AI10" s="6">
-        <v>6</v>
-      </c>
-      <c r="AJ10" s="22">
-        <f t="shared" si="1"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="0"/>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4">
@@ -1578,45 +1314,41 @@
       <c r="R11" s="4">
         <v>4</v>
       </c>
-      <c r="S11" s="16">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="T11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6">
+        <v>14</v>
+      </c>
       <c r="U11" s="6">
-        <v>14</v>
-      </c>
-      <c r="V11" s="6">
-        <v>6</v>
-      </c>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6">
-        <v>4</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6">
+        <v>4</v>
+      </c>
+      <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
       <c r="AA11" s="6"/>
       <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6">
-        <v>4</v>
-      </c>
+      <c r="AC11" s="6">
+        <v>4</v>
+      </c>
+      <c r="AD11" s="6"/>
       <c r="AE11" s="6"/>
       <c r="AF11" s="6"/>
       <c r="AG11" s="6"/>
       <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="22">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI11">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1644,47 +1376,43 @@
       <c r="R12" s="4">
         <v>4</v>
       </c>
-      <c r="S12" s="16">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="T12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6">
+        <v>4</v>
+      </c>
       <c r="U12" s="6">
         <v>4</v>
       </c>
-      <c r="V12" s="6">
-        <v>4</v>
-      </c>
-      <c r="W12" s="6"/>
-      <c r="X12" s="6">
-        <v>4</v>
-      </c>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6">
+        <v>4</v>
+      </c>
+      <c r="X12" s="6"/>
       <c r="Y12" s="6"/>
       <c r="Z12" s="6"/>
       <c r="AA12" s="6"/>
       <c r="AB12" s="6"/>
       <c r="AC12" s="6"/>
-      <c r="AD12" s="6"/>
-      <c r="AE12" s="6">
-        <v>6</v>
-      </c>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6">
-        <v>4</v>
-      </c>
+      <c r="AD12" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="6"/>
       <c r="AH12" s="6"/>
-      <c r="AI12" s="6"/>
-      <c r="AJ12" s="22">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI12">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1710,17 +1438,14 @@
       <c r="R13" s="4">
         <v>4</v>
       </c>
-      <c r="S13" s="16">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
+      <c r="S13" s="6"/>
       <c r="T13" s="6"/>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="6">
-        <v>4</v>
-      </c>
+      <c r="W13" s="6">
+        <v>4</v>
+      </c>
+      <c r="X13" s="6"/>
       <c r="Y13" s="6"/>
       <c r="Z13" s="6"/>
       <c r="AA13" s="6"/>
@@ -1731,18 +1456,17 @@
       <c r="AF13" s="6"/>
       <c r="AG13" s="6"/>
       <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="22">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI13">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C14" s="4">
         <v>4</v>
@@ -1772,20 +1496,17 @@
       </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
-      <c r="S14" s="16">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
+      <c r="S14" s="6"/>
       <c r="T14" s="6"/>
       <c r="U14" s="6"/>
       <c r="V14" s="6"/>
-      <c r="W14" s="6"/>
-      <c r="X14" s="6">
-        <v>4</v>
-      </c>
-      <c r="Y14" s="6">
+      <c r="W14" s="6">
+        <v>4</v>
+      </c>
+      <c r="X14" s="22">
         <v>12</v>
       </c>
+      <c r="Y14" s="6"/>
       <c r="Z14" s="6"/>
       <c r="AA14" s="6"/>
       <c r="AB14" s="6"/>
@@ -1795,18 +1516,17 @@
       <c r="AF14" s="6"/>
       <c r="AG14" s="6"/>
       <c r="AH14" s="6"/>
-      <c r="AI14" s="6"/>
-      <c r="AJ14" s="23">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI14" s="19">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C15" s="4">
         <v>8</v>
@@ -1830,43 +1550,39 @@
       <c r="R15" s="4">
         <v>4</v>
       </c>
-      <c r="S15" s="16">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="T15" s="6">
-        <v>6</v>
-      </c>
+      <c r="S15" s="6">
+        <v>6</v>
+      </c>
+      <c r="T15" s="6"/>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6">
-        <v>4</v>
-      </c>
+      <c r="W15" s="6">
+        <v>4</v>
+      </c>
+      <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
-      <c r="AB15" s="6">
+      <c r="AA15" s="6">
         <v>8</v>
       </c>
+      <c r="AB15" s="6"/>
       <c r="AC15" s="6"/>
       <c r="AD15" s="6"/>
       <c r="AE15" s="6"/>
       <c r="AF15" s="6"/>
       <c r="AG15" s="6"/>
       <c r="AH15" s="6"/>
-      <c r="AI15" s="6"/>
-      <c r="AJ15" s="22">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI15">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C16" s="4">
         <v>4</v>
@@ -1890,10 +1606,7 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
+      <c r="S16" s="6"/>
       <c r="T16" s="6"/>
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
@@ -1909,18 +1622,17 @@
       <c r="AF16" s="6"/>
       <c r="AG16" s="6"/>
       <c r="AH16" s="6"/>
-      <c r="AI16" s="6"/>
-      <c r="AJ16" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI16">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C17" s="4">
         <v>4</v>
@@ -1946,19 +1658,16 @@
       <c r="R17" s="4">
         <v>4</v>
       </c>
-      <c r="S17" s="16">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="T17" s="6">
-        <v>4</v>
-      </c>
+      <c r="S17" s="6">
+        <v>4</v>
+      </c>
+      <c r="T17" s="6"/>
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
-      <c r="W17" s="6"/>
-      <c r="X17" s="6">
-        <v>4</v>
-      </c>
+      <c r="W17" s="6">
+        <v>4</v>
+      </c>
+      <c r="X17" s="6"/>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
       <c r="AA17" s="6"/>
@@ -1969,18 +1678,17 @@
       <c r="AF17" s="6"/>
       <c r="AG17" s="6"/>
       <c r="AH17" s="6"/>
-      <c r="AI17" s="6"/>
-      <c r="AJ17" s="22">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI17">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C18" s="4">
         <v>8</v>
@@ -2016,47 +1724,43 @@
       <c r="R18" s="4">
         <v>6</v>
       </c>
-      <c r="S18" s="16">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="T18" s="6">
-        <v>4</v>
-      </c>
+      <c r="S18" s="6">
+        <v>4</v>
+      </c>
+      <c r="T18" s="6"/>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
+      <c r="W18" s="6">
+        <v>4</v>
+      </c>
       <c r="X18" s="6">
-        <v>4</v>
-      </c>
-      <c r="Y18" s="6">
         <v>8</v>
       </c>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6">
-        <v>6</v>
-      </c>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6">
+        <v>6</v>
+      </c>
+      <c r="AA18" s="6"/>
       <c r="AB18" s="6"/>
-      <c r="AC18" s="6"/>
-      <c r="AD18" s="6">
-        <v>6</v>
-      </c>
+      <c r="AC18" s="6">
+        <v>6</v>
+      </c>
+      <c r="AD18" s="6"/>
       <c r="AE18" s="6"/>
       <c r="AF18" s="6"/>
       <c r="AG18" s="6"/>
       <c r="AH18" s="6"/>
-      <c r="AI18" s="6"/>
-      <c r="AJ18" s="22">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI18">
+        <f t="shared" si="0"/>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C19" s="4">
         <v>4</v>
@@ -2088,45 +1792,41 @@
       <c r="R19" s="4">
         <v>6</v>
       </c>
-      <c r="S19" s="16">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="T19" s="6">
-        <v>4</v>
-      </c>
+      <c r="S19" s="6">
+        <v>4</v>
+      </c>
+      <c r="T19" s="6"/>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6">
-        <v>6</v>
-      </c>
+      <c r="X19" s="6">
+        <v>6</v>
+      </c>
+      <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
       <c r="AA19" s="6"/>
-      <c r="AB19" s="6"/>
+      <c r="AB19" s="6">
+        <v>4</v>
+      </c>
       <c r="AC19" s="6">
         <v>4</v>
       </c>
-      <c r="AD19" s="6">
-        <v>4</v>
-      </c>
+      <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="6"/>
       <c r="AH19" s="6"/>
-      <c r="AI19" s="6"/>
-      <c r="AJ19" s="22">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI19">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>21</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -2148,10 +1848,7 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="16">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
+      <c r="S20" s="6"/>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
@@ -2164,23 +1861,22 @@
       <c r="AC20" s="6"/>
       <c r="AD20" s="6"/>
       <c r="AE20" s="6"/>
-      <c r="AF20" s="6"/>
-      <c r="AG20" s="6">
-        <v>4</v>
-      </c>
+      <c r="AF20" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="6"/>
       <c r="AH20" s="6"/>
-      <c r="AI20" s="6"/>
-      <c r="AJ20" s="22">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI20">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C21" s="4">
         <v>4</v>
@@ -2202,19 +1898,16 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
-      <c r="S21" s="16">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="T21" s="6">
-        <v>4</v>
-      </c>
+      <c r="S21" s="6">
+        <v>4</v>
+      </c>
+      <c r="T21" s="6"/>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
-      <c r="W21" s="6"/>
-      <c r="X21" s="6">
-        <v>4</v>
-      </c>
+      <c r="W21" s="6">
+        <v>4</v>
+      </c>
+      <c r="X21" s="6"/>
       <c r="Y21" s="6"/>
       <c r="Z21" s="6"/>
       <c r="AA21" s="6"/>
@@ -2225,18 +1918,17 @@
       <c r="AF21" s="6"/>
       <c r="AG21" s="6"/>
       <c r="AH21" s="6"/>
-      <c r="AI21" s="6"/>
-      <c r="AJ21" s="22">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI21">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -2260,57 +1952,53 @@
       <c r="R22" s="4">
         <v>4</v>
       </c>
-      <c r="S22" s="16">
-        <f t="shared" si="0"/>
-        <v>12</v>
+      <c r="S22" s="6">
+        <v>4</v>
       </c>
       <c r="T22" s="6">
-        <v>4</v>
-      </c>
-      <c r="U22" s="6">
         <v>14</v>
       </c>
-      <c r="V22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6">
+        <v>4</v>
+      </c>
       <c r="W22" s="6">
         <v>4</v>
       </c>
       <c r="X22" s="6">
         <v>4</v>
       </c>
-      <c r="Y22" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z22" s="6"/>
-      <c r="AA22" s="6">
-        <v>6</v>
-      </c>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="6">
+        <v>6</v>
+      </c>
+      <c r="AA22" s="6"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="6"/>
-      <c r="AD22" s="6"/>
-      <c r="AE22" s="6">
-        <v>4</v>
-      </c>
-      <c r="AF22" s="6"/>
+      <c r="AD22" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6">
+        <v>4</v>
+      </c>
       <c r="AG22" s="6">
         <v>4</v>
       </c>
       <c r="AH22" s="6">
         <v>4</v>
       </c>
-      <c r="AI22" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ22" s="22">
-        <f t="shared" si="1"/>
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI22">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4">
@@ -2334,10 +2022,7 @@
       <c r="R23" s="4">
         <v>4</v>
       </c>
-      <c r="S23" s="16">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
+      <c r="S23" s="6"/>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
@@ -2353,18 +2038,17 @@
       <c r="AF23" s="6"/>
       <c r="AG23" s="6"/>
       <c r="AH23" s="6"/>
-      <c r="AI23" s="6"/>
-      <c r="AJ23" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI23">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4">
@@ -2394,16 +2078,13 @@
       </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
-      <c r="S24" s="16">
-        <f t="shared" si="0"/>
-        <v>30</v>
+      <c r="S24" s="6">
+        <v>4</v>
       </c>
       <c r="T24" s="6">
         <v>4</v>
       </c>
-      <c r="U24" s="6">
-        <v>4</v>
-      </c>
+      <c r="U24" s="6"/>
       <c r="V24" s="6"/>
       <c r="W24" s="6"/>
       <c r="X24" s="6"/>
@@ -2412,29 +2093,28 @@
       <c r="AA24" s="6"/>
       <c r="AB24" s="6"/>
       <c r="AC24" s="6"/>
-      <c r="AD24" s="6"/>
-      <c r="AE24" s="6">
-        <v>4</v>
-      </c>
+      <c r="AD24" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE24" s="6"/>
       <c r="AF24" s="6"/>
-      <c r="AG24" s="6"/>
+      <c r="AG24" s="6">
+        <v>4</v>
+      </c>
       <c r="AH24" s="6">
-        <v>4</v>
-      </c>
-      <c r="AI24" s="6">
-        <v>6</v>
-      </c>
-      <c r="AJ24" s="22">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="AI24">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C25" s="4">
         <v>4</v>
@@ -2462,47 +2142,43 @@
         <v>4</v>
       </c>
       <c r="R25" s="4"/>
-      <c r="S25" s="16">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="T25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6">
+        <v>4</v>
+      </c>
       <c r="U25" s="6">
         <v>4</v>
       </c>
-      <c r="V25" s="6">
-        <v>4</v>
-      </c>
+      <c r="V25" s="6"/>
       <c r="W25" s="6"/>
       <c r="X25" s="6"/>
       <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="6">
-        <v>6</v>
-      </c>
+      <c r="Z25" s="6">
+        <v>6</v>
+      </c>
+      <c r="AA25" s="6"/>
       <c r="AB25" s="6"/>
       <c r="AC25" s="6"/>
-      <c r="AD25" s="6"/>
-      <c r="AE25" s="6">
+      <c r="AD25" s="6">
         <v>8</v>
       </c>
+      <c r="AE25" s="6"/>
       <c r="AF25" s="6"/>
       <c r="AG25" s="6"/>
-      <c r="AH25" s="6"/>
-      <c r="AI25" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ25" s="22">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AH25" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI25">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4">
@@ -2522,22 +2198,19 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
-      <c r="S26" s="16">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="S26" s="6"/>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
       <c r="W26" s="6"/>
-      <c r="X26" s="6"/>
-      <c r="Y26" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="6">
+      <c r="X26" s="6">
+        <v>4</v>
+      </c>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="6">
         <v>8</v>
       </c>
+      <c r="AA26" s="6"/>
       <c r="AB26" s="6"/>
       <c r="AC26" s="6"/>
       <c r="AD26" s="6"/>
@@ -2545,18 +2218,17 @@
       <c r="AF26" s="6"/>
       <c r="AG26" s="6"/>
       <c r="AH26" s="6"/>
-      <c r="AI26" s="6"/>
-      <c r="AJ26" s="22">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI26">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C27" s="4">
         <v>8</v>
@@ -2578,51 +2250,47 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
-      <c r="S27" s="16">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="T27" s="6">
-        <v>4</v>
-      </c>
+      <c r="S27" s="6">
+        <v>4</v>
+      </c>
+      <c r="T27" s="6"/>
       <c r="U27" s="6"/>
       <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
+      <c r="W27" s="6">
+        <v>4</v>
+      </c>
       <c r="X27" s="6">
-        <v>4</v>
-      </c>
-      <c r="Y27" s="6">
         <v>10</v>
       </c>
+      <c r="Y27" s="22">
+        <v>6</v>
+      </c>
       <c r="Z27" s="6">
-        <v>6</v>
-      </c>
-      <c r="AA27" s="6">
         <v>20</v>
       </c>
-      <c r="AB27" s="6"/>
-      <c r="AC27" s="6">
-        <v>6</v>
-      </c>
+      <c r="AA27" s="6"/>
+      <c r="AB27" s="6">
+        <v>6</v>
+      </c>
+      <c r="AC27" s="6"/>
       <c r="AD27" s="6"/>
       <c r="AE27" s="6"/>
       <c r="AF27" s="6"/>
       <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6">
-        <v>6</v>
-      </c>
-      <c r="AJ27" s="23">
-        <f t="shared" si="1"/>
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AH27" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI27" s="19">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>30</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C28" s="4">
         <v>8</v>
@@ -2648,49 +2316,45 @@
       <c r="R28" s="4">
         <v>4</v>
       </c>
-      <c r="S28" s="16">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="T28" s="6">
-        <v>4</v>
-      </c>
+      <c r="S28" s="6">
+        <v>4</v>
+      </c>
+      <c r="T28" s="6"/>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
+      <c r="W28" s="6">
+        <v>4</v>
+      </c>
       <c r="X28" s="6">
         <v>4</v>
       </c>
-      <c r="Y28" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="6">
-        <v>6</v>
-      </c>
-      <c r="AB28" s="6"/>
+      <c r="Y28" s="6"/>
+      <c r="Z28" s="6">
+        <v>6</v>
+      </c>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6">
+        <v>10</v>
+      </c>
       <c r="AC28" s="6">
-        <v>10</v>
-      </c>
-      <c r="AD28" s="6">
-        <v>6</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="AD28" s="6"/>
       <c r="AE28" s="6"/>
       <c r="AF28" s="6"/>
       <c r="AG28" s="6"/>
       <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="22">
-        <f t="shared" si="1"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI28">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -2708,49 +2372,45 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
-      <c r="S29" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="S29" s="6">
+        <v>4</v>
       </c>
       <c r="T29" s="6">
-        <v>4</v>
-      </c>
-      <c r="U29" s="6">
-        <v>6</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U29" s="6"/>
       <c r="V29" s="6"/>
       <c r="W29" s="6"/>
-      <c r="X29" s="6"/>
-      <c r="Y29" s="6">
+      <c r="X29" s="6">
         <v>8</v>
       </c>
-      <c r="Z29" s="6"/>
-      <c r="AA29" s="6">
+      <c r="Y29" s="6"/>
+      <c r="Z29" s="6">
         <v>16</v>
       </c>
+      <c r="AA29" s="6"/>
       <c r="AB29" s="6"/>
       <c r="AC29" s="6"/>
-      <c r="AD29" s="6"/>
-      <c r="AE29" s="6">
+      <c r="AD29" s="6">
         <v>16</v>
       </c>
+      <c r="AE29" s="6"/>
       <c r="AF29" s="6"/>
-      <c r="AG29" s="6"/>
-      <c r="AH29" s="6">
-        <v>6</v>
-      </c>
-      <c r="AI29" s="6"/>
-      <c r="AJ29" s="22">
-        <f t="shared" si="1"/>
+      <c r="AG29" s="6">
+        <v>6</v>
+      </c>
+      <c r="AH29" s="6"/>
+      <c r="AI29">
+        <f t="shared" si="0"/>
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4">
@@ -2770,13 +2430,10 @@
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
-      <c r="S30" s="16">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="T30" s="6">
-        <v>4</v>
-      </c>
+      <c r="S30" s="6">
+        <v>4</v>
+      </c>
+      <c r="T30" s="6"/>
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
       <c r="W30" s="6"/>
@@ -2791,18 +2448,17 @@
       <c r="AF30" s="6"/>
       <c r="AG30" s="6"/>
       <c r="AH30" s="6"/>
-      <c r="AI30" s="6"/>
-      <c r="AJ30" s="22">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI30">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C31" s="4">
         <v>4</v>
@@ -2828,43 +2484,39 @@
       <c r="R31" s="4">
         <v>4</v>
       </c>
-      <c r="S31" s="16">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
+      <c r="S31" s="6"/>
       <c r="T31" s="6"/>
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
       <c r="W31" s="6"/>
-      <c r="X31" s="6"/>
-      <c r="Y31" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z31" s="6"/>
-      <c r="AA31" s="6">
-        <v>6</v>
-      </c>
+      <c r="X31" s="6">
+        <v>4</v>
+      </c>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6">
+        <v>6</v>
+      </c>
+      <c r="AA31" s="6"/>
       <c r="AB31" s="6"/>
       <c r="AC31" s="6"/>
       <c r="AD31" s="6"/>
       <c r="AE31" s="6"/>
       <c r="AF31" s="6"/>
-      <c r="AG31" s="6"/>
-      <c r="AH31" s="6">
-        <v>4</v>
-      </c>
-      <c r="AI31" s="6"/>
-      <c r="AJ31" s="22">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG31" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH31" s="6"/>
+      <c r="AI31">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>36</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -2880,65 +2532,61 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
-      <c r="M32" s="21">
-        <v>6</v>
+      <c r="M32" s="4">
+        <v>4</v>
       </c>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
-      <c r="P32" s="21">
-        <v>4</v>
+      <c r="P32" s="4">
+        <v>6</v>
       </c>
       <c r="Q32" s="4"/>
       <c r="R32" s="4">
         <v>4</v>
       </c>
-      <c r="S32" s="16">
-        <f t="shared" si="0"/>
-        <v>24</v>
+      <c r="S32" s="6">
+        <v>4</v>
       </c>
       <c r="T32" s="6">
-        <v>4</v>
-      </c>
-      <c r="U32" s="6">
-        <v>6</v>
-      </c>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6">
-        <v>6</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="U32" s="6"/>
+      <c r="V32" s="6">
+        <v>6</v>
+      </c>
+      <c r="W32" s="6"/>
       <c r="X32" s="6"/>
       <c r="Y32" s="6"/>
-      <c r="Z32" s="6"/>
-      <c r="AA32" s="6">
-        <v>4</v>
-      </c>
-      <c r="AB32" s="6"/>
-      <c r="AC32" s="6">
-        <v>4</v>
-      </c>
-      <c r="AD32" s="6"/>
-      <c r="AE32" s="6">
+      <c r="Z32" s="6">
+        <v>4</v>
+      </c>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6">
+        <v>4</v>
+      </c>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6">
         <v>10</v>
       </c>
+      <c r="AE32" s="6"/>
       <c r="AF32" s="6"/>
-      <c r="AG32" s="6"/>
+      <c r="AG32" s="6">
+        <v>10</v>
+      </c>
       <c r="AH32" s="6">
-        <v>10</v>
-      </c>
-      <c r="AI32" s="6">
-        <v>6</v>
-      </c>
-      <c r="AJ32" s="22">
-        <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+      <c r="AI32">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>37</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4">
@@ -2958,474 +2606,438 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
-      <c r="S33" s="16">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6">
-        <v>4</v>
-      </c>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6">
-        <v>6</v>
-      </c>
-      <c r="X33" s="6"/>
-      <c r="Y33" s="6">
-        <v>4</v>
-      </c>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6">
+        <v>4</v>
+      </c>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6">
+        <v>6</v>
+      </c>
+      <c r="W33" s="6"/>
+      <c r="X33" s="6">
+        <v>4</v>
+      </c>
+      <c r="Y33" s="6"/>
       <c r="Z33" s="6"/>
       <c r="AA33" s="6"/>
-      <c r="AB33" s="6"/>
-      <c r="AC33" s="6">
-        <v>6</v>
-      </c>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6">
-        <v>4</v>
-      </c>
+      <c r="AB33" s="6">
+        <v>6</v>
+      </c>
+      <c r="AC33" s="6"/>
+      <c r="AD33" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE33" s="6"/>
       <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="6">
-        <v>4</v>
-      </c>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="22">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:36" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="17" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="17">
-        <f>SUM(C4:C33)</f>
+      <c r="AG33" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH33" s="6"/>
+      <c r="AI33">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="B34" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34">
+        <f>SUM(C5:C33)</f>
         <v>64</v>
       </c>
-      <c r="D34" s="17">
-        <f t="shared" ref="D34:AI34" si="2">SUM(D4:D33)</f>
+      <c r="D34">
+        <f t="shared" ref="D34:AH34" si="1">SUM(D5:D33)</f>
         <v>88</v>
       </c>
-      <c r="E34" s="17">
-        <f t="shared" si="2"/>
+      <c r="E34">
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="F34" s="17">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="G34" s="17">
-        <f t="shared" si="2"/>
+      <c r="F34">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="H34" s="17">
-        <f t="shared" si="2"/>
+      <c r="H34">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="I34" s="17">
-        <f t="shared" si="2"/>
+      <c r="I34">
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="J34" s="17">
-        <f t="shared" si="2"/>
+      <c r="J34">
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="K34" s="17">
-        <f t="shared" si="2"/>
+      <c r="K34">
+        <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="L34" s="17">
-        <f t="shared" si="2"/>
+      <c r="L34">
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M34" s="18">
-        <f t="shared" si="2"/>
-        <v>44</v>
-      </c>
-      <c r="N34" s="17">
-        <f t="shared" si="2"/>
+      <c r="M34">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="O34" s="17">
-        <f t="shared" si="2"/>
+      <c r="O34">
+        <f t="shared" si="1"/>
         <v>78</v>
       </c>
-      <c r="P34" s="18">
-        <f t="shared" si="2"/>
-        <v>74</v>
-      </c>
-      <c r="Q34" s="17">
-        <f t="shared" si="2"/>
+      <c r="P34">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="R34" s="17">
-        <f t="shared" si="2"/>
+      <c r="R34">
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="T34" s="17">
-        <f t="shared" si="2"/>
+      <c r="S34">
+        <f t="shared" si="1"/>
         <v>62</v>
       </c>
-      <c r="U34" s="17">
-        <f t="shared" si="2"/>
+      <c r="T34">
+        <f t="shared" si="1"/>
         <v>66</v>
       </c>
-      <c r="V34" s="17">
-        <f t="shared" si="2"/>
+      <c r="U34">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="W34" s="17">
-        <f t="shared" si="2"/>
+      <c r="V34">
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="X34" s="18">
-        <f t="shared" si="2"/>
+      <c r="W34">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="X34" s="21">
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="Y34" s="25">
-        <f t="shared" si="2"/>
+      <c r="Y34" s="21">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="Z34">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="AA34">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="AB34">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AC34">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="AD34">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="AE34">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="AF34">
+        <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="Z34" s="25">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="AA34" s="17">
-        <f t="shared" si="2"/>
-        <v>78</v>
-      </c>
-      <c r="AB34" s="17">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="AC34" s="17">
-        <f t="shared" si="2"/>
-        <v>30</v>
-      </c>
-      <c r="AD34" s="18">
-        <f t="shared" si="2"/>
-        <v>26</v>
-      </c>
-      <c r="AE34" s="17">
-        <f t="shared" si="2"/>
-        <v>52</v>
-      </c>
-      <c r="AF34" s="17">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="AG34" s="17">
-        <f t="shared" si="2"/>
-        <v>64</v>
-      </c>
-      <c r="AH34" s="17">
-        <f t="shared" si="2"/>
+      <c r="AG34">
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="AI34" s="17">
-        <f t="shared" si="2"/>
+      <c r="AH34">
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:36" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
       <c r="B35" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="M35" s="17">
-        <v>42</v>
-      </c>
-      <c r="P35" s="17">
-        <v>76</v>
-      </c>
-      <c r="X35" s="17">
-        <v>60</v>
-      </c>
-      <c r="Y35" s="17">
-        <v>56</v>
-      </c>
-      <c r="Z35" s="17">
-        <v>14</v>
-      </c>
-      <c r="AD35" s="17">
-        <v>30</v>
-      </c>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="B36" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="S1:AH1"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="C1:S1"/>
-    <mergeCell ref="T1:AJ1"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="C1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E81FFC5-23BA-4F97-8AD7-C5B675A827AB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AJ35"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AI35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.625" customWidth="1"/>
+    <col min="1" max="1" width="3.5546875" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="18" width="3.625" customWidth="1"/>
-    <col min="19" max="19" width="3.625" style="17" customWidth="1"/>
-    <col min="20" max="35" width="3.625" customWidth="1"/>
-    <col min="36" max="36" width="3.625" style="17" customWidth="1"/>
+    <col min="3" max="34" width="3.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="31" t="s">
+      <c r="C1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-    </row>
-    <row r="2" spans="1:36" ht="70" x14ac:dyDescent="0.25">
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="16"/>
+      <c r="AC1" s="16"/>
+      <c r="AD1" s="16"/>
+      <c r="AE1" s="16"/>
+      <c r="AF1" s="16"/>
+      <c r="AG1" s="16"/>
+      <c r="AH1" s="16"/>
+    </row>
+    <row r="2" spans="1:35" ht="69.599999999999994" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
-      <c r="B2" s="8"/>
+      <c r="B2" s="8" t="s">
+        <v>3</v>
+      </c>
       <c r="C2" s="9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" s="12"/>
       <c r="I2" s="11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J2" s="12"/>
       <c r="K2" s="11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L2" s="12"/>
       <c r="M2" s="11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N2" s="12"/>
       <c r="O2" s="9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q2" s="12"/>
       <c r="R2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="S2" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="T2" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="U2" s="14"/>
+      <c r="V2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="W2" s="14"/>
+      <c r="X2" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y2" s="14"/>
+      <c r="Z2" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA2" s="14"/>
+      <c r="AB2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC2" s="14"/>
+      <c r="AD2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE2" s="14"/>
+      <c r="AF2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="U2" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="V2" s="14"/>
-      <c r="W2" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="X2" s="14"/>
-      <c r="Y2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF2" s="14"/>
-      <c r="AG2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI2" s="14"/>
-      <c r="AJ2" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AH2" s="14"/>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="S3" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>19</v>
+      </c>
       <c r="T3" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="X3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AA3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AB3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AD3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AF3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AG3" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AH3" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="AI3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ3" s="5"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -3443,7 +3055,7 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-      <c r="S4" s="16"/>
+      <c r="S4" s="6"/>
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
@@ -3459,15 +3071,13 @@
       <c r="AF4" s="6"/>
       <c r="AG4" s="6"/>
       <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
-      <c r="AJ4" s="22"/>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -3495,41 +3105,37 @@
       <c r="R5" s="4">
         <v>4</v>
       </c>
-      <c r="S5" s="16">
-        <f>SUM(C5:R5)</f>
-        <v>20</v>
-      </c>
+      <c r="S5" s="6"/>
       <c r="T5" s="6"/>
       <c r="U5" s="6"/>
       <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6">
-        <v>4</v>
-      </c>
+      <c r="W5" s="6">
+        <v>4</v>
+      </c>
+      <c r="X5" s="6"/>
       <c r="Y5" s="6"/>
       <c r="Z5" s="6"/>
       <c r="AA5" s="6"/>
       <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6">
-        <v>4</v>
-      </c>
+      <c r="AC5" s="6">
+        <v>4</v>
+      </c>
+      <c r="AD5" s="6"/>
       <c r="AE5" s="6"/>
       <c r="AF5" s="6"/>
       <c r="AG5" s="6"/>
       <c r="AH5" s="6"/>
-      <c r="AI5" s="6"/>
-      <c r="AJ5" s="22">
-        <f>SUM(T5:AI5)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI5">
+        <f>SUM(C5:AH5)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -3549,14 +3155,11 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="16">
-        <f t="shared" ref="S6:S33" si="0">SUM(C6:R6)</f>
-        <v>4</v>
-      </c>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6">
-        <v>4</v>
-      </c>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6">
+        <v>4</v>
+      </c>
+      <c r="U6" s="6"/>
       <c r="V6" s="6"/>
       <c r="W6" s="6"/>
       <c r="X6" s="6"/>
@@ -3567,23 +3170,22 @@
       <c r="AC6" s="6"/>
       <c r="AD6" s="6"/>
       <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6">
-        <v>4</v>
-      </c>
+      <c r="AF6" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG6" s="6"/>
       <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="22">
-        <f t="shared" ref="AJ6:AJ33" si="1">SUM(T6:AI6)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI6">
+        <f t="shared" ref="AI6:AI33" si="0">SUM(C6:AH6)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4">
@@ -3617,19 +3219,16 @@
       <c r="R7" s="4">
         <v>4</v>
       </c>
-      <c r="S7" s="16">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="T7" s="6">
-        <v>4</v>
-      </c>
+      <c r="S7" s="6">
+        <v>4</v>
+      </c>
+      <c r="T7" s="6"/>
       <c r="U7" s="6"/>
       <c r="V7" s="6"/>
-      <c r="W7" s="6"/>
-      <c r="X7" s="6">
-        <v>4</v>
-      </c>
+      <c r="W7" s="6">
+        <v>4</v>
+      </c>
+      <c r="X7" s="6"/>
       <c r="Y7" s="6"/>
       <c r="Z7" s="6"/>
       <c r="AA7" s="6"/>
@@ -3637,23 +3236,22 @@
       <c r="AC7" s="6"/>
       <c r="AD7" s="6"/>
       <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6">
+      <c r="AF7" s="6">
         <v>8</v>
       </c>
+      <c r="AG7" s="6"/>
       <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-      <c r="AJ7" s="22">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4">
         <v>4</v>
@@ -3681,13 +3279,10 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
-      <c r="S8" s="16">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="T8" s="6">
-        <v>4</v>
-      </c>
+      <c r="S8" s="6">
+        <v>4</v>
+      </c>
+      <c r="T8" s="6"/>
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
@@ -3699,23 +3294,22 @@
       <c r="AC8" s="6"/>
       <c r="AD8" s="6"/>
       <c r="AE8" s="6"/>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6">
+      <c r="AF8" s="6">
         <v>14</v>
       </c>
+      <c r="AG8" s="6"/>
       <c r="AH8" s="6"/>
-      <c r="AI8" s="6"/>
-      <c r="AJ8" s="22">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI8">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -3741,39 +3335,35 @@
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="16">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
+      <c r="S9" s="6"/>
       <c r="T9" s="6"/>
       <c r="U9" s="6"/>
       <c r="V9" s="6"/>
       <c r="W9" s="6"/>
       <c r="X9" s="6"/>
-      <c r="Y9" s="24">
-        <v>4</v>
-      </c>
+      <c r="Y9" s="6"/>
       <c r="Z9" s="6"/>
       <c r="AA9" s="6"/>
       <c r="AB9" s="6"/>
       <c r="AC9" s="6"/>
       <c r="AD9" s="6"/>
       <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="24"/>
+      <c r="AF9" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="6"/>
       <c r="AH9" s="6"/>
-      <c r="AI9" s="6"/>
-      <c r="AJ9" s="22">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI9">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -3803,17 +3393,14 @@
       </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
-      <c r="S10" s="16">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="T10" s="6">
-        <v>4</v>
-      </c>
-      <c r="U10" s="6"/>
-      <c r="V10" s="6">
-        <v>6</v>
-      </c>
+      <c r="S10" s="6">
+        <v>4</v>
+      </c>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6">
+        <v>6</v>
+      </c>
+      <c r="V10" s="6"/>
       <c r="W10" s="6"/>
       <c r="X10" s="6"/>
       <c r="Y10" s="6"/>
@@ -3822,28 +3409,27 @@
       <c r="AB10" s="6"/>
       <c r="AC10" s="6"/>
       <c r="AD10" s="6"/>
-      <c r="AE10" s="6"/>
-      <c r="AF10" s="24">
-        <v>2</v>
-      </c>
-      <c r="AG10" s="6">
-        <v>6</v>
-      </c>
-      <c r="AH10" s="6"/>
-      <c r="AI10" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ10" s="22">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AE10" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="6">
+        <v>6</v>
+      </c>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -3869,45 +3455,41 @@
       <c r="R11" s="4">
         <v>4</v>
       </c>
-      <c r="S11" s="16">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="T11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6">
+        <v>6</v>
+      </c>
       <c r="U11" s="6">
-        <v>6</v>
-      </c>
-      <c r="V11" s="6">
-        <v>4</v>
-      </c>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6">
-        <v>4</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6">
+        <v>4</v>
+      </c>
+      <c r="X11" s="6"/>
       <c r="Y11" s="6"/>
       <c r="Z11" s="6"/>
       <c r="AA11" s="6"/>
       <c r="AB11" s="6"/>
-      <c r="AC11" s="6"/>
-      <c r="AD11" s="6">
-        <v>4</v>
-      </c>
+      <c r="AC11" s="6">
+        <v>4</v>
+      </c>
+      <c r="AD11" s="6"/>
       <c r="AE11" s="6"/>
       <c r="AF11" s="6"/>
       <c r="AG11" s="6"/>
       <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="22">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI11">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -3933,14 +3515,11 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
-      <c r="S12" s="16">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6">
-        <v>4</v>
-      </c>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6">
+        <v>4</v>
+      </c>
+      <c r="U12" s="6"/>
       <c r="V12" s="6"/>
       <c r="W12" s="6"/>
       <c r="X12" s="6"/>
@@ -3949,37 +3528,36 @@
       <c r="AA12" s="6"/>
       <c r="AB12" s="6"/>
       <c r="AC12" s="6"/>
-      <c r="AD12" s="6"/>
-      <c r="AE12" s="24">
-        <v>6</v>
-      </c>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6">
-        <v>4</v>
-      </c>
+      <c r="AD12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG12" s="6"/>
       <c r="AH12" s="6"/>
-      <c r="AI12" s="6"/>
-      <c r="AJ12" s="22">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI12">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
-      <c r="G13" s="21">
-        <v>4</v>
-      </c>
+      <c r="G13" s="4"/>
       <c r="H13" s="4"/>
-      <c r="I13" s="21"/>
+      <c r="I13" s="4">
+        <v>4</v>
+      </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -3995,17 +3573,14 @@
       <c r="R13" s="4">
         <v>4</v>
       </c>
-      <c r="S13" s="16">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
+      <c r="S13" s="6"/>
       <c r="T13" s="6"/>
       <c r="U13" s="6"/>
       <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="6">
-        <v>4</v>
-      </c>
+      <c r="W13" s="6">
+        <v>4</v>
+      </c>
+      <c r="X13" s="6"/>
       <c r="Y13" s="6"/>
       <c r="Z13" s="6"/>
       <c r="AA13" s="6"/>
@@ -4016,18 +3591,17 @@
       <c r="AF13" s="6"/>
       <c r="AG13" s="6"/>
       <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="22">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI13">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4">
@@ -4055,18 +3629,15 @@
       </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
-      <c r="S14" s="16">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
+      <c r="S14" s="6"/>
       <c r="T14" s="6"/>
       <c r="U14" s="6"/>
       <c r="V14" s="6"/>
       <c r="W14" s="6"/>
-      <c r="X14" s="6"/>
-      <c r="Y14" s="6">
-        <v>4</v>
-      </c>
+      <c r="X14" s="6">
+        <v>4</v>
+      </c>
+      <c r="Y14" s="6"/>
       <c r="Z14" s="6"/>
       <c r="AA14" s="6"/>
       <c r="AB14" s="6"/>
@@ -4076,18 +3647,17 @@
       <c r="AF14" s="6"/>
       <c r="AG14" s="6"/>
       <c r="AH14" s="6"/>
-      <c r="AI14" s="6"/>
-      <c r="AJ14" s="22">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI14">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C15" s="4">
         <v>4</v>
@@ -4111,43 +3681,39 @@
       <c r="R15" s="4">
         <v>4</v>
       </c>
-      <c r="S15" s="16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="T15" s="6">
-        <v>4</v>
-      </c>
+      <c r="S15" s="6">
+        <v>4</v>
+      </c>
+      <c r="T15" s="6"/>
       <c r="U15" s="6"/>
       <c r="V15" s="6"/>
-      <c r="W15" s="6"/>
-      <c r="X15" s="6">
-        <v>4</v>
-      </c>
+      <c r="W15" s="6">
+        <v>4</v>
+      </c>
+      <c r="X15" s="6"/>
       <c r="Y15" s="6"/>
       <c r="Z15" s="6"/>
-      <c r="AA15" s="6"/>
-      <c r="AB15" s="6">
-        <v>4</v>
-      </c>
+      <c r="AA15" s="6">
+        <v>4</v>
+      </c>
+      <c r="AB15" s="6"/>
       <c r="AC15" s="6"/>
       <c r="AD15" s="6"/>
       <c r="AE15" s="6"/>
       <c r="AF15" s="6"/>
       <c r="AG15" s="6"/>
       <c r="AH15" s="6"/>
-      <c r="AI15" s="6"/>
-      <c r="AJ15" s="22">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI15">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C16" s="4">
         <v>4</v>
@@ -4167,10 +3733,7 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="16">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="S16" s="6"/>
       <c r="T16" s="6"/>
       <c r="U16" s="6"/>
       <c r="V16" s="6"/>
@@ -4186,18 +3749,17 @@
       <c r="AF16" s="6"/>
       <c r="AG16" s="6"/>
       <c r="AH16" s="6"/>
-      <c r="AI16" s="6"/>
-      <c r="AJ16" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI16">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C17" s="4">
         <v>4</v>
@@ -4221,17 +3783,14 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
-      <c r="S17" s="16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
+      <c r="S17" s="6"/>
       <c r="T17" s="6"/>
       <c r="U17" s="6"/>
       <c r="V17" s="6"/>
-      <c r="W17" s="6"/>
-      <c r="X17" s="6">
-        <v>4</v>
-      </c>
+      <c r="W17" s="6">
+        <v>4</v>
+      </c>
+      <c r="X17" s="6"/>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6"/>
       <c r="AA17" s="6"/>
@@ -4242,18 +3801,17 @@
       <c r="AF17" s="6"/>
       <c r="AG17" s="6"/>
       <c r="AH17" s="6"/>
-      <c r="AI17" s="6"/>
-      <c r="AJ17" s="22">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI17">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C18" s="4">
         <v>4</v>
@@ -4289,45 +3847,41 @@
       <c r="R18" s="4">
         <v>4</v>
       </c>
-      <c r="S18" s="16">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="T18" s="6">
-        <v>4</v>
-      </c>
+      <c r="S18" s="6">
+        <v>4</v>
+      </c>
+      <c r="T18" s="6"/>
       <c r="U18" s="6"/>
       <c r="V18" s="6"/>
       <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6">
-        <v>4</v>
-      </c>
+      <c r="X18" s="6">
+        <v>4</v>
+      </c>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="6"/>
       <c r="AB18" s="6"/>
-      <c r="AC18" s="6"/>
-      <c r="AD18" s="6">
-        <v>4</v>
-      </c>
+      <c r="AC18" s="6">
+        <v>4</v>
+      </c>
+      <c r="AD18" s="6"/>
       <c r="AE18" s="6"/>
       <c r="AF18" s="6"/>
       <c r="AG18" s="6"/>
       <c r="AH18" s="6"/>
-      <c r="AI18" s="6"/>
-      <c r="AJ18" s="22">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI18">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4">
@@ -4355,41 +3909,37 @@
       <c r="R19" s="4">
         <v>4</v>
       </c>
-      <c r="S19" s="16">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
+      <c r="S19" s="6"/>
       <c r="T19" s="6"/>
       <c r="U19" s="6"/>
       <c r="V19" s="6"/>
       <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="24">
-        <v>6</v>
-      </c>
+      <c r="X19" s="22">
+        <v>6</v>
+      </c>
+      <c r="Y19" s="6"/>
       <c r="Z19" s="6"/>
       <c r="AA19" s="6"/>
       <c r="AB19" s="6"/>
-      <c r="AC19" s="6"/>
-      <c r="AD19" s="6">
-        <v>4</v>
-      </c>
+      <c r="AC19" s="6">
+        <v>4</v>
+      </c>
+      <c r="AD19" s="6"/>
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
       <c r="AG19" s="6"/>
       <c r="AH19" s="6"/>
-      <c r="AI19" s="6"/>
-      <c r="AJ19" s="22">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI19" s="19">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>21</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -4411,10 +3961,7 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="16">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
+      <c r="S20" s="6"/>
       <c r="T20" s="6"/>
       <c r="U20" s="6"/>
       <c r="V20" s="6"/>
@@ -4430,18 +3977,17 @@
       <c r="AF20" s="6"/>
       <c r="AG20" s="6"/>
       <c r="AH20" s="6"/>
-      <c r="AI20" s="6"/>
-      <c r="AJ20" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI20">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C21" s="4">
         <v>4</v>
@@ -4463,17 +4009,14 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
-      <c r="S21" s="16">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
+      <c r="S21" s="6"/>
       <c r="T21" s="6"/>
       <c r="U21" s="6"/>
       <c r="V21" s="6"/>
-      <c r="W21" s="6"/>
-      <c r="X21" s="6">
-        <v>4</v>
-      </c>
+      <c r="W21" s="6">
+        <v>4</v>
+      </c>
+      <c r="X21" s="6"/>
       <c r="Y21" s="6"/>
       <c r="Z21" s="6"/>
       <c r="AA21" s="6"/>
@@ -4484,18 +4027,17 @@
       <c r="AF21" s="6"/>
       <c r="AG21" s="6"/>
       <c r="AH21" s="6"/>
-      <c r="AI21" s="6"/>
-      <c r="AJ21" s="22">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI21">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -4517,45 +4059,41 @@
       <c r="R22" s="4">
         <v>4</v>
       </c>
-      <c r="S22" s="16">
-        <f t="shared" si="0"/>
+      <c r="S22" s="6">
+        <v>4</v>
+      </c>
+      <c r="T22" s="6">
         <v>8</v>
       </c>
-      <c r="T22" s="6">
-        <v>4</v>
-      </c>
-      <c r="U22" s="24">
-        <v>4</v>
-      </c>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6">
-        <v>4</v>
-      </c>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6">
+        <v>4</v>
+      </c>
+      <c r="W22" s="6"/>
       <c r="X22" s="6"/>
       <c r="Y22" s="6"/>
       <c r="Z22" s="6"/>
       <c r="AA22" s="6"/>
       <c r="AB22" s="6"/>
       <c r="AC22" s="6"/>
-      <c r="AD22" s="6"/>
-      <c r="AE22" s="24">
-        <v>8</v>
-      </c>
+      <c r="AD22" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE22" s="6"/>
       <c r="AF22" s="6"/>
       <c r="AG22" s="6"/>
       <c r="AH22" s="6"/>
-      <c r="AI22" s="6"/>
-      <c r="AJ22" s="22">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI22">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4">
@@ -4579,10 +4117,7 @@
       <c r="R23" s="4">
         <v>4</v>
       </c>
-      <c r="S23" s="16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
+      <c r="S23" s="6"/>
       <c r="T23" s="6"/>
       <c r="U23" s="6"/>
       <c r="V23" s="6"/>
@@ -4598,18 +4133,17 @@
       <c r="AF23" s="6"/>
       <c r="AG23" s="6"/>
       <c r="AH23" s="6"/>
-      <c r="AI23" s="6"/>
-      <c r="AJ23" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI23">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4">
@@ -4635,13 +4169,10 @@
       </c>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
-      <c r="S24" s="16">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="T24" s="6">
-        <v>4</v>
-      </c>
+      <c r="S24" s="6">
+        <v>4</v>
+      </c>
+      <c r="T24" s="6"/>
       <c r="U24" s="6"/>
       <c r="V24" s="6"/>
       <c r="W24" s="6"/>
@@ -4651,29 +4182,28 @@
       <c r="AA24" s="6"/>
       <c r="AB24" s="6"/>
       <c r="AC24" s="6"/>
-      <c r="AD24" s="6"/>
-      <c r="AE24" s="6">
-        <v>4</v>
-      </c>
+      <c r="AD24" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE24" s="6"/>
       <c r="AF24" s="6"/>
-      <c r="AG24" s="6"/>
+      <c r="AG24" s="6">
+        <v>4</v>
+      </c>
       <c r="AH24" s="6">
         <v>4</v>
       </c>
-      <c r="AI24" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ24" s="22">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI24">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C25" s="4">
         <v>4</v>
@@ -4697,43 +4227,39 @@
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
-      <c r="S25" s="16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
+      <c r="S25" s="6"/>
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
       <c r="V25" s="6"/>
       <c r="W25" s="6"/>
       <c r="X25" s="6"/>
       <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="6">
-        <v>4</v>
-      </c>
+      <c r="Z25" s="6">
+        <v>4</v>
+      </c>
+      <c r="AA25" s="6"/>
       <c r="AB25" s="6"/>
       <c r="AC25" s="6"/>
-      <c r="AD25" s="6"/>
-      <c r="AE25" s="6">
-        <v>4</v>
-      </c>
+      <c r="AD25" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE25" s="6"/>
       <c r="AF25" s="6"/>
       <c r="AG25" s="6"/>
-      <c r="AH25" s="6"/>
-      <c r="AI25" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ25" s="22">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AH25" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4">
@@ -4753,20 +4279,17 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
-      <c r="S26" s="16">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="S26" s="6"/>
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
       <c r="W26" s="6"/>
       <c r="X26" s="6"/>
       <c r="Y26" s="6"/>
-      <c r="Z26" s="6"/>
-      <c r="AA26" s="6">
-        <v>4</v>
-      </c>
+      <c r="Z26" s="6">
+        <v>4</v>
+      </c>
+      <c r="AA26" s="6"/>
       <c r="AB26" s="6"/>
       <c r="AC26" s="6"/>
       <c r="AD26" s="6"/>
@@ -4774,18 +4297,17 @@
       <c r="AF26" s="6"/>
       <c r="AG26" s="6"/>
       <c r="AH26" s="6"/>
-      <c r="AI26" s="6"/>
-      <c r="AJ26" s="22">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI26">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C27" s="4">
         <v>4</v>
@@ -4807,47 +4329,43 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
-      <c r="S27" s="16">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
+      <c r="S27" s="6"/>
       <c r="T27" s="6"/>
       <c r="U27" s="6"/>
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
-      <c r="X27" s="6"/>
+      <c r="X27" s="6">
+        <v>4</v>
+      </c>
       <c r="Y27" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Z27" s="6">
-        <v>6</v>
-      </c>
-      <c r="AA27" s="6">
         <v>8</v>
       </c>
-      <c r="AB27" s="6"/>
-      <c r="AC27" s="6">
-        <v>4</v>
-      </c>
+      <c r="AA27" s="6"/>
+      <c r="AB27" s="6">
+        <v>4</v>
+      </c>
+      <c r="AC27" s="6"/>
       <c r="AD27" s="6"/>
       <c r="AE27" s="6"/>
       <c r="AF27" s="6"/>
       <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ27" s="22">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AH27" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI27">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>30</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C28" s="4">
         <v>4</v>
@@ -4871,49 +4389,45 @@
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
-      <c r="S28" s="16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="T28" s="6">
-        <v>4</v>
-      </c>
+      <c r="S28" s="6">
+        <v>4</v>
+      </c>
+      <c r="T28" s="6"/>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
+      <c r="W28" s="6">
+        <v>4</v>
+      </c>
       <c r="X28" s="6">
         <v>4</v>
       </c>
-      <c r="Y28" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="6">
-        <v>4</v>
-      </c>
-      <c r="AB28" s="6"/>
+      <c r="Y28" s="6"/>
+      <c r="Z28" s="6">
+        <v>4</v>
+      </c>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6">
+        <v>8</v>
+      </c>
       <c r="AC28" s="6">
-        <v>8</v>
-      </c>
-      <c r="AD28" s="6">
-        <v>4</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AD28" s="6"/>
       <c r="AE28" s="6"/>
       <c r="AF28" s="6"/>
       <c r="AG28" s="6"/>
       <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="22">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI28">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>32</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -4931,49 +4445,45 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
       <c r="R29" s="4"/>
-      <c r="S29" s="16">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="S29" s="6">
+        <v>4</v>
       </c>
       <c r="T29" s="6">
         <v>4</v>
       </c>
-      <c r="U29" s="6">
-        <v>4</v>
-      </c>
+      <c r="U29" s="6"/>
       <c r="V29" s="6"/>
       <c r="W29" s="6"/>
-      <c r="X29" s="6"/>
-      <c r="Y29" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z29" s="6"/>
-      <c r="AA29" s="6">
+      <c r="X29" s="6">
+        <v>4</v>
+      </c>
+      <c r="Y29" s="6"/>
+      <c r="Z29" s="6">
         <v>8</v>
       </c>
+      <c r="AA29" s="6"/>
       <c r="AB29" s="6"/>
       <c r="AC29" s="6"/>
-      <c r="AD29" s="6"/>
-      <c r="AE29" s="6">
+      <c r="AD29" s="6">
         <v>10</v>
       </c>
+      <c r="AE29" s="6"/>
       <c r="AF29" s="6"/>
-      <c r="AG29" s="6"/>
-      <c r="AH29" s="6">
-        <v>4</v>
-      </c>
-      <c r="AI29" s="6"/>
-      <c r="AJ29" s="22">
-        <f t="shared" si="1"/>
+      <c r="AG29" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH29" s="6"/>
+      <c r="AI29">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4">
@@ -4993,10 +4503,7 @@
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
-      <c r="S30" s="16">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="S30" s="6"/>
       <c r="T30" s="6"/>
       <c r="U30" s="6"/>
       <c r="V30" s="6"/>
@@ -5012,18 +4519,17 @@
       <c r="AF30" s="6"/>
       <c r="AG30" s="6"/>
       <c r="AH30" s="6"/>
-      <c r="AI30" s="6"/>
-      <c r="AJ30" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI30">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C31" s="4">
         <v>4</v>
@@ -5047,43 +4553,39 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
       <c r="R31" s="4"/>
-      <c r="S31" s="16">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
+      <c r="S31" s="6"/>
       <c r="T31" s="6"/>
       <c r="U31" s="6"/>
       <c r="V31" s="6"/>
       <c r="W31" s="6"/>
-      <c r="X31" s="6"/>
-      <c r="Y31" s="6">
-        <v>4</v>
-      </c>
-      <c r="Z31" s="6"/>
-      <c r="AA31" s="6">
-        <v>4</v>
-      </c>
+      <c r="X31" s="6">
+        <v>4</v>
+      </c>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6">
+        <v>4</v>
+      </c>
+      <c r="AA31" s="6"/>
       <c r="AB31" s="6"/>
       <c r="AC31" s="6"/>
       <c r="AD31" s="6"/>
       <c r="AE31" s="6"/>
       <c r="AF31" s="6"/>
-      <c r="AG31" s="6"/>
-      <c r="AH31" s="6">
-        <v>4</v>
-      </c>
-      <c r="AI31" s="6"/>
-      <c r="AJ31" s="22">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG31" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH31" s="6"/>
+      <c r="AI31">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>36</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -5107,49 +4609,45 @@
       <c r="R32" s="4">
         <v>4</v>
       </c>
-      <c r="S32" s="16">
-        <f t="shared" si="0"/>
-        <v>12</v>
+      <c r="S32" s="6">
+        <v>4</v>
       </c>
       <c r="T32" s="6">
         <v>4</v>
       </c>
-      <c r="U32" s="6">
-        <v>4</v>
-      </c>
+      <c r="U32" s="6"/>
       <c r="V32" s="6"/>
       <c r="W32" s="6"/>
       <c r="X32" s="6"/>
       <c r="Y32" s="6"/>
       <c r="Z32" s="6"/>
       <c r="AA32" s="6"/>
-      <c r="AB32" s="6"/>
-      <c r="AC32" s="6">
-        <v>4</v>
-      </c>
-      <c r="AD32" s="6"/>
-      <c r="AE32" s="6">
-        <v>6</v>
-      </c>
+      <c r="AB32" s="6">
+        <v>4</v>
+      </c>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE32" s="6"/>
       <c r="AF32" s="6"/>
-      <c r="AG32" s="6"/>
+      <c r="AG32" s="6">
+        <v>4</v>
+      </c>
       <c r="AH32" s="6">
         <v>4</v>
       </c>
-      <c r="AI32" s="6">
-        <v>4</v>
-      </c>
-      <c r="AJ32" s="22">
-        <f t="shared" si="1"/>
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AI32">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>37</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C33" s="4"/>
       <c r="D33" s="4">
@@ -5169,198 +4667,170 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
-      <c r="S33" s="16">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
+      <c r="S33" s="6"/>
       <c r="T33" s="6"/>
       <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6">
-        <v>4</v>
-      </c>
-      <c r="X33" s="6"/>
-      <c r="Y33" s="6">
-        <v>4</v>
-      </c>
+      <c r="V33" s="6">
+        <v>4</v>
+      </c>
+      <c r="W33" s="6"/>
+      <c r="X33" s="6">
+        <v>4</v>
+      </c>
+      <c r="Y33" s="6"/>
       <c r="Z33" s="6"/>
       <c r="AA33" s="6"/>
-      <c r="AB33" s="6"/>
-      <c r="AC33" s="6">
-        <v>4</v>
-      </c>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6">
-        <v>4</v>
-      </c>
+      <c r="AB33" s="6">
+        <v>4</v>
+      </c>
+      <c r="AC33" s="6"/>
+      <c r="AD33" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE33" s="6"/>
       <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="6">
-        <v>4</v>
-      </c>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="22">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="B34" s="19" t="s">
-        <v>51</v>
-      </c>
+      <c r="AG33" s="6">
+        <v>4</v>
+      </c>
+      <c r="AH33" s="6"/>
+      <c r="AI33">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.3">
       <c r="C34">
         <f>SUM(C5:C33)</f>
         <v>40</v>
       </c>
       <c r="D34">
-        <f t="shared" ref="D34:AI34" si="2">SUM(D5:D33)</f>
+        <f t="shared" ref="D34:AH34" si="1">SUM(D5:D33)</f>
         <v>60</v>
       </c>
       <c r="E34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="F34">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="G34" s="15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="K34">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="L34">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="M34">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="R34">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="U34">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="V34">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="W34">
+        <f t="shared" si="1"/>
+        <v>32</v>
+      </c>
+      <c r="X34" s="19">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="Y34">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="Z34">
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="H34">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="I34" s="15">
-        <f t="shared" si="2"/>
+      <c r="AA34">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AB34">
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="J34">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="2"/>
+      <c r="AC34">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="AD34">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="AE34">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="AF34">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="AG34">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="AH34">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="X35" s="21">
         <v>32</v>
-      </c>
-      <c r="L34">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="M34">
-        <f t="shared" si="2"/>
-        <v>24</v>
-      </c>
-      <c r="N34">
-        <f t="shared" si="2"/>
-        <v>16</v>
-      </c>
-      <c r="O34">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="P34">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-      <c r="Q34">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="R34">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="T34">
-        <f t="shared" si="2"/>
-        <v>40</v>
-      </c>
-      <c r="U34" s="15">
-        <f t="shared" si="2"/>
-        <v>26</v>
-      </c>
-      <c r="V34">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="W34">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="X34">
-        <f t="shared" si="2"/>
-        <v>32</v>
-      </c>
-      <c r="Y34" s="15">
-        <f t="shared" si="2"/>
-        <v>38</v>
-      </c>
-      <c r="Z34">
-        <f t="shared" si="2"/>
-        <v>6</v>
-      </c>
-      <c r="AA34">
-        <f t="shared" si="2"/>
-        <v>36</v>
-      </c>
-      <c r="AB34">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="AC34">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="AD34">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="AE34" s="15">
-        <f t="shared" si="2"/>
-        <v>42</v>
-      </c>
-      <c r="AF34" s="15">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="AG34" s="15">
-        <f t="shared" si="2"/>
-        <v>36</v>
-      </c>
-      <c r="AH34">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="AI34">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="B35" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G35">
-        <v>32</v>
-      </c>
-      <c r="I35">
-        <v>24</v>
-      </c>
-      <c r="U35">
-        <v>30</v>
-      </c>
-      <c r="Y35">
-        <v>32</v>
-      </c>
-      <c r="AE35">
-        <v>36</v>
-      </c>
-      <c r="AF35">
-        <v>4</v>
-      </c>
-      <c r="AG35">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -5368,18 +4838,18 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="X2:Y2"/>
+    <mergeCell ref="Z2:AA2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="V2:W2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="S1:AH1"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AH2:AI2"/>
-    <mergeCell ref="C1:S1"/>
-    <mergeCell ref="T1:AJ1"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AD2:AE2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="C1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
